--- a/data/extracted/inventory-receipts/CONTENEDOR QATAR PREMIUM PX 09 JUNIO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR QATAR PREMIUM PX 09 JUNIO.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA67CB0-7B25-49BA-863E-ED89B13CDC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9135"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3923,7 +3936,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3964,12 +3977,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4249,50 +4261,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L1020"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4330,12 +4342,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4373,7 +4385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4411,7 +4423,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4449,7 +4461,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4487,7 +4499,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4525,7 +4537,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4563,7 +4575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4601,7 +4613,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4639,7 +4651,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4677,7 +4689,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4715,7 +4727,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4753,7 +4765,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4791,7 +4803,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4829,7 +4841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4867,7 +4879,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4905,7 +4917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4943,7 +4955,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -4981,7 +4993,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -5019,7 +5031,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -5057,7 +5069,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -5095,7 +5107,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -5133,7 +5145,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -5171,7 +5183,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5209,7 +5221,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5247,7 +5259,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5285,7 +5297,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5323,7 +5335,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5361,7 +5373,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5399,7 +5411,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5437,7 +5449,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5475,7 +5487,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5513,7 +5525,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5551,7 +5563,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5589,7 +5601,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5639,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -5665,7 +5677,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -5703,7 +5715,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5741,7 +5753,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5779,7 +5791,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5817,7 +5829,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5855,7 +5867,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5893,7 +5905,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5931,7 +5943,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -5969,7 +5981,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -6007,7 +6019,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -6045,7 +6057,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -6083,7 +6095,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -6121,7 +6133,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -6159,7 +6171,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -6197,7 +6209,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6235,7 +6247,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6273,7 +6285,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6311,7 +6323,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6349,7 +6361,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6387,7 +6399,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6425,7 +6437,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F62" s="1" t="s">
         <v>135</v>
       </c>
@@ -6445,7 +6457,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F63" s="1" t="s">
         <v>137</v>
       </c>
@@ -6465,7 +6477,7 @@
         <v>1285.8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6503,7 +6515,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -6541,7 +6553,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -6579,7 +6591,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6617,7 +6629,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6655,7 +6667,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6693,7 +6705,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6731,7 +6743,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6769,7 +6781,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6807,7 +6819,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6845,7 +6857,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6883,7 +6895,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6921,7 +6933,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -6959,7 +6971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -6997,7 +7009,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -7035,7 +7047,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -7073,7 +7085,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -7111,7 +7123,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -7149,7 +7161,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -7187,7 +7199,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7225,7 +7237,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7263,7 +7275,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7301,7 +7313,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7339,7 +7351,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7377,7 +7389,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7415,7 +7427,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7453,7 +7465,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7491,7 +7503,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7529,7 +7541,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7567,7 +7579,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7605,7 +7617,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7643,7 +7655,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7681,7 +7693,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7719,7 +7731,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7757,7 +7769,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F98" s="1" t="s">
         <v>135</v>
       </c>
@@ -7777,7 +7789,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F99" s="1" t="s">
         <v>175</v>
       </c>
@@ -7797,7 +7809,7 @@
         <v>789.3</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7835,7 +7847,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -7873,7 +7885,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -7911,7 +7923,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -7949,7 +7961,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -7987,7 +7999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -8025,7 +8037,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -8063,7 +8075,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8101,7 +8113,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -8139,7 +8151,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8177,7 +8189,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8215,7 +8227,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8253,7 +8265,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8291,7 +8303,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8329,7 +8341,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8367,7 +8379,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8405,7 +8417,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8443,7 +8455,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8481,7 +8493,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8519,7 +8531,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8557,7 +8569,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8595,7 +8607,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8633,7 +8645,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8671,7 +8683,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8709,7 +8721,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8747,7 +8759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8785,7 +8797,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8823,7 +8835,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8861,7 +8873,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8899,7 +8911,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -8937,7 +8949,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -8975,7 +8987,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -9013,7 +9025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -9051,7 +9063,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -9089,7 +9101,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -9127,7 +9139,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9165,7 +9177,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9203,7 +9215,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9241,7 +9253,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9279,7 +9291,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9317,7 +9329,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9355,7 +9367,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9393,7 +9405,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9431,7 +9443,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9469,7 +9481,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9507,7 +9519,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9545,7 +9557,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9583,7 +9595,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9621,7 +9633,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9659,7 +9671,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9697,7 +9709,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9735,7 +9747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9773,7 +9785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9811,7 +9823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9849,7 +9861,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9887,7 +9899,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -9925,7 +9937,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -9963,7 +9975,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -10001,7 +10013,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -10039,7 +10051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -10077,7 +10089,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -10115,7 +10127,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -10153,7 +10165,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10191,7 +10203,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10229,7 +10241,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10267,7 +10279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10305,7 +10317,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10343,7 +10355,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10381,7 +10393,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10419,7 +10431,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10457,7 +10469,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10495,7 +10507,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10533,7 +10545,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10571,7 +10583,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10609,7 +10621,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10647,7 +10659,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10685,7 +10697,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10723,7 +10735,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10761,7 +10773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10799,7 +10811,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10837,7 +10849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10875,7 +10887,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -10913,7 +10925,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -10951,7 +10963,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -10989,7 +11001,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -11027,7 +11039,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -11065,7 +11077,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -11103,7 +11115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -11141,7 +11153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -11179,7 +11191,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -11217,7 +11229,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11255,7 +11267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11293,7 +11305,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11331,7 +11343,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11369,7 +11381,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11407,7 +11419,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11445,7 +11457,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11483,7 +11495,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11521,7 +11533,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11559,7 +11571,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11597,7 +11609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11635,7 +11647,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11673,7 +11685,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11711,7 +11723,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11749,7 +11761,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11787,7 +11799,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11825,7 +11837,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11863,7 +11875,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11901,7 +11913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -11939,7 +11951,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -11977,7 +11989,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -12015,7 +12027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -12053,7 +12065,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -12091,7 +12103,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -12129,7 +12141,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -12167,7 +12179,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -12205,7 +12217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12243,7 +12255,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12281,7 +12293,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12319,7 +12331,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12357,7 +12369,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12395,7 +12407,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12433,7 +12445,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12471,7 +12483,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -12509,7 +12521,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -12547,7 +12559,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12585,7 +12597,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12623,7 +12635,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12661,7 +12673,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F228" s="1" t="s">
         <v>135</v>
       </c>
@@ -12681,7 +12693,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F229" s="1" t="s">
         <v>380</v>
       </c>
@@ -12701,7 +12713,7 @@
         <v>3025.5</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12739,7 +12751,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12777,7 +12789,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12815,7 +12827,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12853,7 +12865,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -12891,7 +12903,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -12929,7 +12941,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -12967,7 +12979,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -13005,7 +13017,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -13043,7 +13055,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -13081,7 +13093,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -13119,7 +13131,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -13157,7 +13169,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -13195,7 +13207,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13233,7 +13245,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13271,7 +13283,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -13309,7 +13321,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -13347,7 +13359,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13385,7 +13397,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13423,7 +13435,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13461,7 +13473,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13499,7 +13511,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13537,7 +13549,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F252" s="1" t="s">
         <v>135</v>
       </c>
@@ -13557,7 +13569,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F253" s="1" t="s">
         <v>67</v>
       </c>
@@ -13577,7 +13589,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13615,7 +13627,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13653,7 +13665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13691,7 +13703,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -13729,7 +13741,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -13767,7 +13779,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -13805,7 +13817,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -13843,7 +13855,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -13881,7 +13893,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -13919,7 +13931,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -13957,7 +13969,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -13995,7 +14007,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -14033,7 +14045,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -14071,7 +14083,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -14109,7 +14121,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -14147,7 +14159,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -14185,7 +14197,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -14223,7 +14235,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14261,7 +14273,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14299,7 +14311,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14337,7 +14349,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14375,7 +14387,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14413,7 +14425,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14451,7 +14463,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14489,7 +14501,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14527,7 +14539,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14565,7 +14577,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14603,7 +14615,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14641,7 +14653,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14679,7 +14691,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14717,7 +14729,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14755,7 +14767,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14793,7 +14805,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14831,7 +14843,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14869,7 +14881,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F288" s="1" t="s">
         <v>135</v>
       </c>
@@ -14889,7 +14901,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F289" s="1" t="s">
         <v>91</v>
       </c>
@@ -14909,7 +14921,7 @@
         <v>793.79999999999984</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -14947,7 +14959,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -14985,7 +14997,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -15023,7 +15035,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -15061,7 +15073,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -15099,7 +15111,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -15137,7 +15149,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -15175,7 +15187,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15213,7 +15225,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15251,7 +15263,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15289,7 +15301,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15327,7 +15339,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15365,7 +15377,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15403,7 +15415,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15441,7 +15453,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15479,7 +15491,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15517,7 +15529,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15555,7 +15567,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15593,7 +15605,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15631,7 +15643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15669,7 +15681,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15707,7 +15719,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15745,7 +15757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15783,7 +15795,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15821,7 +15833,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15859,7 +15871,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -15897,7 +15909,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -15935,7 +15947,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -15973,7 +15985,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -16011,7 +16023,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -16049,7 +16061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -16087,7 +16099,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -16125,7 +16137,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -16163,7 +16175,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16201,7 +16213,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16239,7 +16251,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16277,7 +16289,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16315,7 +16327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16353,7 +16365,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16391,7 +16403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16429,7 +16441,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16467,7 +16479,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16505,7 +16517,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16543,7 +16555,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16581,7 +16593,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16619,7 +16631,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16657,7 +16669,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16695,7 +16707,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16733,7 +16745,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16771,7 +16783,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -16809,7 +16821,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -16847,7 +16859,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -16885,7 +16897,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -16923,7 +16935,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -16961,7 +16973,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -16999,7 +17011,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -17037,7 +17049,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -17075,7 +17087,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -17113,7 +17125,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -17151,7 +17163,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17189,7 +17201,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -17227,7 +17239,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -17265,7 +17277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17303,7 +17315,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17341,7 +17353,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17379,7 +17391,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17417,7 +17429,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17455,7 +17467,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17493,7 +17505,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17531,7 +17543,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17569,7 +17581,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17607,7 +17619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17645,7 +17657,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17683,7 +17695,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17721,7 +17733,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17759,7 +17771,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17797,7 +17809,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17835,7 +17847,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17873,7 +17885,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -17911,7 +17923,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -17949,7 +17961,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -17987,7 +17999,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -18025,7 +18037,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -18063,7 +18075,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -18101,7 +18113,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -18139,7 +18151,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -18177,7 +18189,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18215,7 +18227,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18253,7 +18265,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18291,7 +18303,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18329,7 +18341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>19</v>
       </c>
@@ -18367,7 +18379,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -18405,7 +18417,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18443,7 +18455,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18481,7 +18493,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18519,7 +18531,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18557,7 +18569,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18595,7 +18607,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18633,7 +18645,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18671,7 +18683,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18709,7 +18721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18747,7 +18759,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18785,7 +18797,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18823,7 +18835,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18861,7 +18873,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18899,7 +18911,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -18937,7 +18949,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -18975,7 +18987,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -19013,7 +19025,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -19051,7 +19063,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -19089,7 +19101,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -19127,7 +19139,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -19165,7 +19177,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -19203,7 +19215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19241,7 +19253,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19279,7 +19291,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19317,7 +19329,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19355,7 +19367,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19393,7 +19405,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19431,7 +19443,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19469,7 +19481,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19507,7 +19519,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19545,7 +19557,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19583,7 +19595,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19621,7 +19633,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19659,7 +19671,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19697,7 +19709,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19735,7 +19747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19773,7 +19785,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19811,7 +19823,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19849,7 +19861,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19887,7 +19899,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -19925,7 +19937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -19963,7 +19975,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -20001,7 +20013,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -20039,7 +20051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -20077,7 +20089,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -20115,7 +20127,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -20153,7 +20165,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -20191,7 +20203,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20229,7 +20241,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20267,7 +20279,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20305,7 +20317,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20343,7 +20355,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20381,7 +20393,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20419,7 +20431,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20457,7 +20469,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20495,7 +20507,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20533,7 +20545,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F438" s="1" t="s">
         <v>135</v>
       </c>
@@ -20553,7 +20565,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F439" s="1" t="s">
         <v>614</v>
       </c>
@@ -20573,7 +20585,7 @@
         <v>3507.6</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20611,7 +20623,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20649,7 +20661,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -20687,7 +20699,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -20725,7 +20737,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20763,7 +20775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20801,7 +20813,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20839,7 +20851,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -20877,7 +20889,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -20915,7 +20927,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -20953,7 +20965,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -20991,7 +21003,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -21029,7 +21041,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -21067,7 +21079,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -21105,7 +21117,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -21143,7 +21155,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -21181,7 +21193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -21219,7 +21231,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21257,7 +21269,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21295,7 +21307,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21333,7 +21345,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21371,7 +21383,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -21409,7 +21421,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -21447,7 +21459,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21485,7 +21497,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21523,7 +21535,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21561,7 +21573,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21599,7 +21611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21637,7 +21649,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21675,7 +21687,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21713,7 +21725,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21751,7 +21763,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21789,7 +21801,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21827,7 +21839,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21865,7 +21877,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21903,7 +21915,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -21941,7 +21953,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -21979,7 +21991,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -22017,7 +22029,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -22055,7 +22067,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -22093,7 +22105,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -22131,7 +22143,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -22169,7 +22181,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -22207,7 +22219,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22245,7 +22257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22283,7 +22295,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22321,7 +22333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22359,7 +22371,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22397,7 +22409,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22435,7 +22447,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -22473,7 +22485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -22511,7 +22523,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22549,7 +22561,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22587,7 +22599,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22625,7 +22637,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F494" s="1" t="s">
         <v>135</v>
       </c>
@@ -22645,7 +22657,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F495" s="1" t="s">
         <v>672</v>
       </c>
@@ -22665,7 +22677,7 @@
         <v>1279.0999999999999</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22703,7 +22715,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22741,7 +22753,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22779,7 +22791,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22817,7 +22829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22855,7 +22867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -22893,7 +22905,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -22931,7 +22943,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -22969,7 +22981,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -23007,7 +23019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -23045,7 +23057,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -23083,7 +23095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -23121,7 +23133,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -23159,7 +23171,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23197,7 +23209,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23235,7 +23247,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23273,7 +23285,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23311,7 +23323,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23349,7 +23361,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23387,7 +23399,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23425,7 +23437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23463,7 +23475,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23501,7 +23513,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23539,7 +23551,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23577,7 +23589,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23615,7 +23627,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23653,7 +23665,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23691,7 +23703,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23729,7 +23741,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23767,7 +23779,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23805,7 +23817,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23843,7 +23855,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -23881,7 +23893,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -23919,7 +23931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -23957,7 +23969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -23995,7 +24007,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -24033,7 +24045,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -24071,7 +24083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -24109,7 +24121,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -24147,7 +24159,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -24185,7 +24197,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24223,7 +24235,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24261,7 +24273,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24299,7 +24311,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24337,7 +24349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24375,7 +24387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24413,7 +24425,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24451,7 +24463,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24489,7 +24501,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24527,7 +24539,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24565,7 +24577,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -24603,7 +24615,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -24641,7 +24653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24679,7 +24691,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24717,7 +24729,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24755,7 +24767,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24793,7 +24805,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24831,7 +24843,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24869,7 +24881,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24907,7 +24919,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -24945,7 +24957,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -24983,7 +24995,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -25021,7 +25033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -25059,7 +25071,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -25097,7 +25109,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -25135,7 +25147,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -25173,7 +25185,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25211,7 +25223,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25249,7 +25261,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25287,7 +25299,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25325,7 +25337,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25363,7 +25375,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25401,7 +25413,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25439,7 +25451,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25477,7 +25489,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25515,7 +25527,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25553,7 +25565,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25591,7 +25603,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25629,7 +25641,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25667,7 +25679,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25705,7 +25717,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25743,7 +25755,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25781,7 +25793,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25819,7 +25831,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25857,7 +25869,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25895,7 +25907,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -25933,7 +25945,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -25971,7 +25983,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -26009,7 +26021,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -26047,7 +26059,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -26085,7 +26097,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -26123,7 +26135,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -26161,7 +26173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26199,7 +26211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26237,7 +26249,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26275,7 +26287,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26313,7 +26325,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26351,7 +26363,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26389,7 +26401,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26427,7 +26439,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26465,7 +26477,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26503,7 +26515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26541,7 +26553,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -26579,7 +26591,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>19</v>
       </c>
@@ -26617,7 +26629,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26655,7 +26667,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26693,7 +26705,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26731,7 +26743,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26769,7 +26781,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26807,7 +26819,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26845,7 +26857,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26883,7 +26895,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -26921,7 +26933,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -26959,7 +26971,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -26997,7 +27009,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -27035,7 +27047,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -27073,7 +27085,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -27111,7 +27123,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -27149,7 +27161,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -27187,7 +27199,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27225,7 +27237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27263,7 +27275,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27301,7 +27313,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27339,7 +27351,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27377,7 +27389,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27415,7 +27427,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27453,7 +27465,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27491,7 +27503,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27529,7 +27541,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27567,7 +27579,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -27605,7 +27617,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>19</v>
       </c>
@@ -27643,7 +27655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27681,7 +27693,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27719,7 +27731,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27757,7 +27769,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27795,7 +27807,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27833,7 +27845,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27871,7 +27883,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27909,7 +27921,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -27947,7 +27959,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -27985,7 +27997,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -28023,7 +28035,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -28061,7 +28073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -28099,7 +28111,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -28137,7 +28149,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -28175,7 +28187,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28213,7 +28225,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28251,7 +28263,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28289,7 +28301,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28327,7 +28339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28365,7 +28377,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28403,7 +28415,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28441,7 +28453,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28479,7 +28491,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28517,7 +28529,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28555,7 +28567,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28593,7 +28605,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28631,7 +28643,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28669,7 +28681,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28707,7 +28719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28745,7 +28757,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28783,7 +28795,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28821,7 +28833,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28859,7 +28871,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28897,7 +28909,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -28935,7 +28947,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -28973,7 +28985,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -29011,7 +29023,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -29049,7 +29061,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -29087,7 +29099,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -29125,7 +29137,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -29163,7 +29175,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29201,7 +29213,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29239,7 +29251,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29277,7 +29289,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29315,7 +29327,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29353,7 +29365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29391,7 +29403,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29429,7 +29441,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29467,7 +29479,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29505,7 +29517,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29543,7 +29555,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29581,7 +29593,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29619,7 +29631,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29657,7 +29669,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29695,7 +29707,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29733,7 +29745,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29771,7 +29783,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29809,7 +29821,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29847,7 +29859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29885,7 +29897,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -29923,7 +29935,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -29961,7 +29973,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -29999,7 +30011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -30037,7 +30049,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -30075,7 +30087,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -30113,7 +30125,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -30151,7 +30163,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30189,7 +30201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>19</v>
       </c>
@@ -30227,7 +30239,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>19</v>
       </c>
@@ -30265,7 +30277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30303,7 +30315,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30341,7 +30353,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30379,7 +30391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30417,7 +30429,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30455,7 +30467,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30493,7 +30505,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30531,7 +30543,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30569,7 +30581,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30607,7 +30619,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30645,7 +30657,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30683,7 +30695,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30721,7 +30733,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30759,7 +30771,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30797,7 +30809,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30835,7 +30847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30873,7 +30885,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -30911,7 +30923,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -30949,7 +30961,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -30987,7 +30999,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -31025,7 +31037,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -31063,7 +31075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -31101,7 +31113,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -31139,7 +31151,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -31177,7 +31189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -31215,7 +31227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31253,7 +31265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31291,7 +31303,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31329,7 +31341,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31367,7 +31379,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31405,7 +31417,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31443,7 +31455,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31481,7 +31493,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31519,7 +31531,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31557,7 +31569,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31595,7 +31607,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>19</v>
       </c>
@@ -31633,7 +31645,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -31671,7 +31683,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31709,7 +31721,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31747,7 +31759,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31785,7 +31797,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31823,7 +31835,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31861,7 +31873,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31899,7 +31911,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -31937,7 +31949,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -31975,7 +31987,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -32013,7 +32025,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -32051,7 +32063,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -32089,7 +32101,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -32127,7 +32139,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -32165,7 +32177,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -32203,7 +32215,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -32241,7 +32253,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32279,7 +32291,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32317,7 +32329,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32355,7 +32367,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32393,7 +32405,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F752" s="1" t="s">
         <v>135</v>
       </c>
@@ -32413,7 +32425,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F753" s="1" t="s">
         <v>1038</v>
       </c>
@@ -32436,7 +32448,7 @@
         <v>6268.9999999999991</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32474,7 +32486,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>19</v>
       </c>
@@ -32512,7 +32524,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>19</v>
       </c>
@@ -32550,7 +32562,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32588,7 +32600,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32626,7 +32638,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32664,7 +32676,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32702,7 +32714,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32740,7 +32752,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32778,7 +32790,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32816,7 +32828,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32854,7 +32866,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -32892,7 +32904,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -32930,7 +32942,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -32968,7 +32980,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -33006,7 +33018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -33044,7 +33056,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -33082,7 +33094,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>19</v>
       </c>
@@ -33120,7 +33132,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>19</v>
       </c>
@@ -33158,7 +33170,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -33196,7 +33208,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -33234,7 +33246,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33272,7 +33284,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33310,7 +33322,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33348,7 +33360,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33386,7 +33398,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33424,7 +33436,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33462,7 +33474,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33500,7 +33512,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33538,7 +33550,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F783" s="1" t="s">
         <v>135</v>
       </c>
@@ -33558,7 +33570,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F784" s="1" t="s">
         <v>1072</v>
       </c>
@@ -33578,7 +33590,7 @@
         <v>664.3</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33616,7 +33628,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33654,7 +33666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33692,7 +33704,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33730,7 +33742,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33768,7 +33780,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33806,7 +33818,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>19</v>
       </c>
@@ -33844,7 +33856,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>19</v>
       </c>
@@ -33882,7 +33894,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -33920,7 +33932,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -33958,7 +33970,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>19</v>
       </c>
@@ -33996,7 +34008,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>19</v>
       </c>
@@ -34034,7 +34046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -34072,7 +34084,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -34110,7 +34122,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -34148,7 +34160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -34186,7 +34198,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -34224,7 +34236,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -34262,7 +34274,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34300,7 +34312,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34338,7 +34350,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34376,7 +34388,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34414,7 +34426,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34452,7 +34464,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34490,7 +34502,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34528,7 +34540,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34566,7 +34578,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34604,7 +34616,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34642,7 +34654,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34680,7 +34692,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34718,7 +34730,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34756,7 +34768,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34794,7 +34806,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34832,7 +34844,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -34870,7 +34882,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -34908,7 +34920,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -34946,7 +34958,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -34984,7 +34996,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -35022,7 +35034,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -35060,7 +35072,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -35098,7 +35110,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -35136,7 +35148,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -35174,7 +35186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -35212,7 +35224,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>19</v>
       </c>
@@ -35250,7 +35262,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>19</v>
       </c>
@@ -35288,7 +35300,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35326,7 +35338,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35364,7 +35376,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35402,7 +35414,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35440,7 +35452,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35478,7 +35490,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35516,7 +35528,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35554,7 +35566,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>19</v>
       </c>
@@ -35592,7 +35604,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>19</v>
       </c>
@@ -35630,7 +35642,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35668,7 +35680,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35706,7 +35718,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>19</v>
       </c>
@@ -35744,7 +35756,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>19</v>
       </c>
@@ -35782,7 +35794,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35820,7 +35832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35858,7 +35870,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -35896,7 +35908,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -35934,7 +35946,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -35972,7 +35984,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -36010,7 +36022,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F849" s="1" t="s">
         <v>135</v>
       </c>
@@ -36030,7 +36042,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F850" s="1" t="s">
         <v>1140</v>
       </c>
@@ -36050,7 +36062,7 @@
         <v>1502.3</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" s="1" t="s">
         <v>19</v>
       </c>
@@ -36088,7 +36100,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" s="1" t="s">
         <v>19</v>
       </c>
@@ -36126,7 +36138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>19</v>
       </c>
@@ -36164,7 +36176,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>19</v>
       </c>
@@ -36202,7 +36214,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -36240,7 +36252,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36278,7 +36290,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36316,7 +36328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36354,7 +36366,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36392,7 +36404,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36430,7 +36442,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>19</v>
       </c>
@@ -36468,7 +36480,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>19</v>
       </c>
@@ -36506,7 +36518,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36544,7 +36556,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36582,7 +36594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>19</v>
       </c>
@@ -36620,7 +36632,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>19</v>
       </c>
@@ -36658,7 +36670,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36696,7 +36708,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36734,7 +36746,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36772,7 +36784,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36810,7 +36822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36848,7 +36860,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -36886,7 +36898,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -36924,7 +36936,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -36962,7 +36974,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" s="1" t="s">
         <v>19</v>
       </c>
@@ -37000,7 +37012,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" s="1" t="s">
         <v>19</v>
       </c>
@@ -37038,7 +37050,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -37076,7 +37088,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -37114,7 +37126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -37152,7 +37164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -37190,7 +37202,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -37228,7 +37240,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37266,7 +37278,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37304,7 +37316,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37342,7 +37354,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37380,7 +37392,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37418,7 +37430,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37456,7 +37468,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37494,7 +37506,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>19</v>
       </c>
@@ -37532,7 +37544,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>19</v>
       </c>
@@ -37570,7 +37582,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37608,7 +37620,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F892" s="1" t="s">
         <v>135</v>
       </c>
@@ -37628,7 +37640,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F893" s="1" t="s">
         <v>1184</v>
       </c>
@@ -37648,7 +37660,7 @@
         <v>956.9</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37686,7 +37698,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37724,7 +37736,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>19</v>
       </c>
@@ -37762,7 +37774,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>19</v>
       </c>
@@ -37800,7 +37812,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37838,7 +37850,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37876,7 +37888,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -37914,7 +37926,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -37952,7 +37964,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -37990,7 +38002,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -38028,7 +38040,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -38066,7 +38078,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -38104,7 +38116,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -38142,7 +38154,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>19</v>
       </c>
@@ -38180,7 +38192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>19</v>
       </c>
@@ -38218,7 +38230,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -38256,7 +38268,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38294,7 +38306,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>19</v>
       </c>
@@ -38332,7 +38344,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>19</v>
       </c>
@@ -38370,7 +38382,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>19</v>
       </c>
@@ -38408,7 +38420,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>19</v>
       </c>
@@ -38446,7 +38458,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>19</v>
       </c>
@@ -38484,7 +38496,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>19</v>
       </c>
@@ -38522,7 +38534,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>19</v>
       </c>
@@ -38560,7 +38572,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>19</v>
       </c>
@@ -38598,7 +38610,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" s="1" t="s">
         <v>19</v>
       </c>
@@ -38636,7 +38648,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" s="1" t="s">
         <v>19</v>
       </c>
@@ -38674,7 +38686,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" s="1" t="s">
         <v>19</v>
       </c>
@@ -38712,7 +38724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A922" s="1" t="s">
         <v>19</v>
       </c>
@@ -38750,7 +38762,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" s="1" t="s">
         <v>19</v>
       </c>
@@ -38788,7 +38800,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>19</v>
       </c>
@@ -38826,7 +38838,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A925" s="1" t="s">
         <v>19</v>
       </c>
@@ -38864,7 +38876,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A926" s="1" t="s">
         <v>19</v>
       </c>
@@ -38902,7 +38914,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" s="1" t="s">
         <v>19</v>
       </c>
@@ -38940,7 +38952,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A928" s="1" t="s">
         <v>19</v>
       </c>
@@ -38978,7 +38990,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A929" s="1" t="s">
         <v>19</v>
       </c>
@@ -39016,7 +39028,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A930" s="1" t="s">
         <v>19</v>
       </c>
@@ -39054,7 +39066,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A931" s="1" t="s">
         <v>19</v>
       </c>
@@ -39092,7 +39104,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" s="1" t="s">
         <v>19</v>
       </c>
@@ -39130,7 +39142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" s="1" t="s">
         <v>19</v>
       </c>
@@ -39168,7 +39180,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A934" s="1" t="s">
         <v>19</v>
       </c>
@@ -39206,7 +39218,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" s="1" t="s">
         <v>19</v>
       </c>
@@ -39244,7 +39256,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F936" s="1" t="s">
         <v>135</v>
       </c>
@@ -39264,7 +39276,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F937" s="1" t="s">
         <v>107</v>
       </c>
@@ -39281,7 +39293,7 @@
         <v>1001.6000000000001</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" s="1" t="s">
         <v>19</v>
       </c>
@@ -39319,7 +39331,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" s="1" t="s">
         <v>19</v>
       </c>
@@ -39357,7 +39369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A940" s="1" t="s">
         <v>19</v>
       </c>
@@ -39395,7 +39407,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" s="1" t="s">
         <v>19</v>
       </c>
@@ -39433,7 +39445,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" s="1" t="s">
         <v>19</v>
       </c>
@@ -39471,7 +39483,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A943" s="1" t="s">
         <v>19</v>
       </c>
@@ -39509,7 +39521,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" s="1" t="s">
         <v>19</v>
       </c>
@@ -39547,7 +39559,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" s="1" t="s">
         <v>19</v>
       </c>
@@ -39585,7 +39597,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A946" s="1" t="s">
         <v>19</v>
       </c>
@@ -39623,7 +39635,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" s="1" t="s">
         <v>19</v>
       </c>
@@ -39661,7 +39673,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A948" s="1" t="s">
         <v>19</v>
       </c>
@@ -39699,7 +39711,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A949" s="1" t="s">
         <v>19</v>
       </c>
@@ -39737,7 +39749,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" s="1" t="s">
         <v>19</v>
       </c>
@@ -39775,7 +39787,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A951" s="1" t="s">
         <v>19</v>
       </c>
@@ -39813,7 +39825,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A952" s="1" t="s">
         <v>19</v>
       </c>
@@ -39851,7 +39863,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A953" s="1" t="s">
         <v>19</v>
       </c>
@@ -39889,7 +39901,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A954" s="1" t="s">
         <v>19</v>
       </c>
@@ -39927,7 +39939,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A955" s="1" t="s">
         <v>19</v>
       </c>
@@ -39965,7 +39977,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" s="1" t="s">
         <v>19</v>
       </c>
@@ -40003,7 +40015,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A957" s="1" t="s">
         <v>19</v>
       </c>
@@ -40041,7 +40053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A958" s="1" t="s">
         <v>19</v>
       </c>
@@ -40079,7 +40091,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" s="1" t="s">
         <v>19</v>
       </c>
@@ -40117,7 +40129,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F960" s="1" t="s">
         <v>135</v>
       </c>
@@ -40137,7 +40149,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F961" s="1" t="s">
         <v>67</v>
       </c>
@@ -40154,7 +40166,7 @@
         <v>518.29999999999995</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" s="1" t="s">
         <v>19</v>
       </c>
@@ -40192,7 +40204,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A963" s="1" t="s">
         <v>19</v>
       </c>
@@ -40230,7 +40242,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A964" s="1" t="s">
         <v>19</v>
       </c>
@@ -40268,7 +40280,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" s="1" t="s">
         <v>19</v>
       </c>
@@ -40306,7 +40318,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A966" s="1" t="s">
         <v>19</v>
       </c>
@@ -40344,7 +40356,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A967" s="1" t="s">
         <v>19</v>
       </c>
@@ -40382,7 +40394,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A968" s="1" t="s">
         <v>19</v>
       </c>
@@ -40420,7 +40432,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A969" s="1" t="s">
         <v>19</v>
       </c>
@@ -40458,7 +40470,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A970" s="1" t="s">
         <v>19</v>
       </c>
@@ -40496,7 +40508,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A971" s="1" t="s">
         <v>19</v>
       </c>
@@ -40534,7 +40546,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A972" s="1" t="s">
         <v>19</v>
       </c>
@@ -40572,7 +40584,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A973" s="1" t="s">
         <v>19</v>
       </c>
@@ -40610,7 +40622,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A974" s="1" t="s">
         <v>19</v>
       </c>
@@ -40648,7 +40660,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A975" s="1" t="s">
         <v>19</v>
       </c>
@@ -40686,7 +40698,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A976" s="1" t="s">
         <v>19</v>
       </c>
@@ -40724,7 +40736,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A977" s="1" t="s">
         <v>19</v>
       </c>
@@ -40762,7 +40774,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A978" s="1" t="s">
         <v>19</v>
       </c>
@@ -40800,7 +40812,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A979" s="1" t="s">
         <v>19</v>
       </c>
@@ -40838,7 +40850,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A980" s="1" t="s">
         <v>19</v>
       </c>
@@ -40876,7 +40888,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A981" s="1" t="s">
         <v>19</v>
       </c>
@@ -40914,7 +40926,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A982" s="1" t="s">
         <v>19</v>
       </c>
@@ -40952,7 +40964,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A983" s="1" t="s">
         <v>19</v>
       </c>
@@ -40990,7 +41002,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F984" s="1" t="s">
         <v>135</v>
       </c>
@@ -41010,7 +41022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F985" s="1" t="s">
         <v>67</v>
       </c>
@@ -41030,7 +41042,7 @@
         <v>515.20000000000005</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F986" s="1" t="s">
         <v>135</v>
       </c>
@@ -41050,7 +41062,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A987" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41088,7 +41100,7 @@
         <v>74.7</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F988" s="1" t="s">
         <v>135</v>
       </c>
@@ -41108,7 +41120,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A989" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41146,7 +41158,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F990" s="1" t="s">
         <v>135</v>
       </c>
@@ -41166,7 +41178,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A991" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41204,7 +41216,7 @@
         <v>170.4</v>
       </c>
     </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F992" s="1" t="s">
         <v>135</v>
       </c>
@@ -41224,7 +41236,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A993" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41262,7 +41274,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F994" s="1" t="s">
         <v>135</v>
       </c>
@@ -41282,7 +41294,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A995" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41320,7 +41332,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F996" s="1" t="s">
         <v>135</v>
       </c>
@@ -41340,7 +41352,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A997" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41378,7 +41390,7 @@
         <v>209.7</v>
       </c>
     </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F998" s="1" t="s">
         <v>135</v>
       </c>
@@ -41398,7 +41410,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A999" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41436,7 +41448,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="1000" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1000" s="1" t="s">
         <v>135</v>
       </c>
@@ -41456,7 +41468,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1001" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1001" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41494,7 +41506,7 @@
         <v>358.6</v>
       </c>
     </row>
-    <row r="1002" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1002" s="1" t="s">
         <v>135</v>
       </c>
@@ -41514,7 +41526,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1003" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1003" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41552,7 +41564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1004" s="1" t="s">
         <v>135</v>
       </c>
@@ -41572,7 +41584,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1005" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1005" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41610,7 +41622,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="1006" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1006" s="1" t="s">
         <v>135</v>
       </c>
@@ -41630,7 +41642,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1007" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1007" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41668,7 +41680,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="1008" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1008" s="1" t="s">
         <v>135</v>
       </c>
@@ -41688,7 +41700,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1009" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1009" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41726,7 +41738,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="1010" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1010" s="1" t="s">
         <v>135</v>
       </c>
@@ -41746,7 +41758,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1011" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1011" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41784,7 +41796,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="1012" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1012" s="1" t="s">
         <v>135</v>
       </c>
@@ -41804,7 +41816,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1013" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1013" s="1" t="s">
         <v>1280</v>
       </c>
@@ -41842,7 +41854,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="1014" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1014" s="1" t="s">
         <v>135</v>
       </c>
@@ -41862,7 +41874,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="1015" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1015"/>
       <c r="B1015"/>
       <c r="C1015"/>
@@ -41876,7 +41888,7 @@
       <c r="K1015"/>
       <c r="L1015"/>
     </row>
-    <row r="1016" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1016"/>
       <c r="B1016"/>
       <c r="C1016"/>
@@ -41890,7 +41902,7 @@
       <c r="K1016"/>
       <c r="L1016"/>
     </row>
-    <row r="1017" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1017"/>
       <c r="B1017"/>
       <c r="C1017"/>
@@ -41904,7 +41916,7 @@
       <c r="K1017"/>
       <c r="L1017"/>
     </row>
-    <row r="1018" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1018"/>
       <c r="B1018"/>
       <c r="C1018"/>
@@ -41918,7 +41930,7 @@
       <c r="K1018"/>
       <c r="L1018"/>
     </row>
-    <row r="1019" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1019"/>
       <c r="B1019"/>
       <c r="C1019"/>
@@ -41932,7 +41944,7 @@
       <c r="K1019"/>
       <c r="L1019"/>
     </row>
-    <row r="1020" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1020"/>
       <c r="B1020"/>
       <c r="C1020"/>
@@ -41950,4 +41962,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FADA58F-6A4F-4994-AC61-2E2915FCFBCA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>48150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>